--- a/Dataset.xlsx
+++ b/Dataset.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="medical" sheetId="1" r:id="rId1"/>
@@ -12,10 +12,10 @@
     <sheet name="financial" sheetId="2" r:id="rId3"/>
     <sheet name="computer_science" sheetId="3" r:id="rId4"/>
     <sheet name="legal" sheetId="4" r:id="rId5"/>
-    <sheet name="biomedical" sheetId="5" r:id="rId6"/>
-    <sheet name="code" sheetId="6" r:id="rId7"/>
-    <sheet name="academic" sheetId="7" r:id="rId8"/>
-    <sheet name="physics" sheetId="8" r:id="rId9"/>
+    <sheet name="code" sheetId="6" r:id="rId6"/>
+    <sheet name="academic" sheetId="7" r:id="rId7"/>
+    <sheet name="physics" sheetId="8" r:id="rId8"/>
+    <sheet name="biomedical" sheetId="5" r:id="rId9"/>
     <sheet name="chemistry" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="156">
   <si>
     <t>medalpaca/medical_meadow_medical_flashcards</t>
   </si>
@@ -216,9 +216,6 @@
     <t>sys_response</t>
   </si>
   <si>
-    <t>ethicalabs/computer-says-no</t>
-  </si>
-  <si>
     <t>completion</t>
   </si>
   <si>
@@ -274,6 +271,231 @@
   </si>
   <si>
     <t>prithivMLmods/Math-Solve</t>
+  </si>
+  <si>
+    <t>MAsad789565/Coding_GPT4_Data</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>assistant</t>
+  </si>
+  <si>
+    <t>Aratako/Synthetic-JP-EN-Coding-Dataset-801k-50k</t>
+  </si>
+  <si>
+    <t>Sky-T/Roblox-luau-coding_L1</t>
+  </si>
+  <si>
+    <t>EyaZr/coding</t>
+  </si>
+  <si>
+    <t>ethanker/agentic_coding_dataset</t>
+  </si>
+  <si>
+    <t>Tapos-Minmoy/python_programming_QA</t>
+  </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>bachtruoq/python_QA_train</t>
+  </si>
+  <si>
+    <t>rodrigoramosrs/dotnet</t>
+  </si>
+  <si>
+    <t>dmeldrum6/PHP_Master_QA_Dataset</t>
+  </si>
+  <si>
+    <t>KhawlaQuraan/QA_python</t>
+  </si>
+  <si>
+    <t>premkumarelangovan/AcademicStaxParaphrase</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>c11634/academichumanization</t>
+  </si>
+  <si>
+    <t>dpeelen9/academic-flashcards</t>
+  </si>
+  <si>
+    <t>DisgustingOzil/Academic_dataset_ShortQA</t>
+  </si>
+  <si>
+    <t>DisgustingOzil/Academic_MCQ_Dataset</t>
+  </si>
+  <si>
+    <t>c123ian/kan_academy_q_a</t>
+  </si>
+  <si>
+    <t>allenai/openbookqa</t>
+  </si>
+  <si>
+    <t>question_stem</t>
+  </si>
+  <si>
+    <t>fact1</t>
+  </si>
+  <si>
+    <t>qinchuanhui/UDA-QA</t>
+  </si>
+  <si>
+    <t>AcademieDuNumerique/atos-eviden-curator-qa</t>
+  </si>
+  <si>
+    <t>c123ian/alpaca_khan_acad_comments_1000</t>
+  </si>
+  <si>
+    <t>maximus-21/PhysicsQA</t>
+  </si>
+  <si>
+    <t>mlfoundations-dev/stackexchange_physics</t>
+  </si>
+  <si>
+    <t>mingye94/textbookreasoning_physics</t>
+  </si>
+  <si>
+    <t>mlfoundations-dev/a1_science_camel_physics</t>
+  </si>
+  <si>
+    <t>instruction_seed</t>
+  </si>
+  <si>
+    <t>deepseek_solution</t>
+  </si>
+  <si>
+    <t>mlfoundations-dev/a1_science_stackexchange_physics</t>
+  </si>
+  <si>
+    <t>ayoubkirouane/arxiv-physics</t>
+  </si>
+  <si>
+    <t>vinhtran2611/ArtifactAI_arxiv-physics-instruct-tune-30k_formated</t>
+  </si>
+  <si>
+    <t>mathieussr/arxiv-physics_DPO</t>
+  </si>
+  <si>
+    <t>chosen</t>
+  </si>
+  <si>
+    <t>gallen881/arxiv-physics</t>
+  </si>
+  <si>
+    <t>message_1</t>
+  </si>
+  <si>
+    <t>message_2</t>
+  </si>
+  <si>
+    <t>andersonbcdefg/physics</t>
+  </si>
+  <si>
+    <t>MohammadKhodadad/multi-lingual-chemical-qac</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>Kylan12/mycotoxin-chemical-research-sythetic-reasoning</t>
+  </si>
+  <si>
+    <t>Jaafer/Chemical_question_definition</t>
+  </si>
+  <si>
+    <t>Jaafer/ChemicalData</t>
+  </si>
+  <si>
+    <t>ChemicalName</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Sourabh2/chemical_compund</t>
+  </si>
+  <si>
+    <t>supergoose/flan_combined_task1483_chemical_extraction_chemprot_dataset</t>
+  </si>
+  <si>
+    <t>targets</t>
+  </si>
+  <si>
+    <t>mlfoundations-dev/stackexchange_chemistry</t>
+  </si>
+  <si>
+    <t>jablonkagroup/chemistry_stackexchange</t>
+  </si>
+  <si>
+    <t>raw_data</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>dim/camel_ai_chemistry</t>
+  </si>
+  <si>
+    <t>jonlecumberri/camel_chemistry_openqa</t>
+  </si>
+  <si>
+    <t>kirubel1738/biology-qa</t>
+  </si>
+  <si>
+    <t>herronej/SciTrust2-BiologyQA</t>
+  </si>
+  <si>
+    <t>mlfoundations-dev/a1_science_camel_biology</t>
+  </si>
+  <si>
+    <t>mlfoundations-dev/a1_science_arxiv_biology</t>
+  </si>
+  <si>
+    <t>LLMTeamAkiyama/cleaned_ToT-Biology</t>
+  </si>
+  <si>
+    <t>mlfoundations-dev/camel_biology_gpt-4o-mini_1x</t>
+  </si>
+  <si>
+    <t>camel-ai/biology</t>
+  </si>
+  <si>
+    <t>HydraLM/biology_dataset_alpaca</t>
+  </si>
+  <si>
+    <t>Team-Promptia/Qwen2.5-7B-RLT-medicine_biology-expert_data_generation</t>
+  </si>
+  <si>
+    <t>LLMTeamAkiyama/cleand_moremilk_ToT-Biology</t>
+  </si>
+  <si>
+    <t>team-bay/data-science-qa</t>
+  </si>
+  <si>
+    <t>soufyane/DATA_SCIENCE_QA</t>
+  </si>
+  <si>
+    <t>RazinAleks/SO-Python_QA-Data_Science_and_Machine_Learning_class</t>
+  </si>
+  <si>
+    <t>additional</t>
+  </si>
+  <si>
+    <t>feta</t>
+  </si>
+  <si>
+    <t>corpus</t>
   </si>
 </sst>
 </file>
@@ -771,7 +993,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -789,6 +1011,152 @@
       </c>
       <c r="E1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -927,7 +1295,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -1042,7 +1410,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -1110,7 +1478,7 @@
         <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1148,7 +1516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.6640625" bestFit="1" customWidth="1"/>
@@ -1271,16 +1639,44 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1315,7 +1711,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -1324,12 +1720,12 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -1343,7 +1739,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -1357,7 +1753,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -1371,21 +1767,21 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>70</v>
       </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -1399,7 +1795,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -1413,7 +1809,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -1427,7 +1823,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
@@ -1439,24 +1835,24 @@
         <v>21</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
         <v>78</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1467,8 +1863,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1485,6 +1884,146 @@
       </c>
       <c r="E1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +2033,187 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="36.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="D12" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1514,31 +2233,144 @@
         <v>27</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1548,7 +2380,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1568,6 +2400,146 @@
         <v>27</v>
       </c>
     </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
